--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/14.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/14.xlsx
@@ -426,13 +426,13 @@
         <v>-9.9665122464517</v>
       </c>
       <c r="E2">
-        <v>-23.96243587371732</v>
+        <v>-26.54942174855318</v>
       </c>
       <c r="F2">
-        <v>-3.518754111472498</v>
+        <v>-3.467034992678711</v>
       </c>
       <c r="G2">
-        <v>-15.66407083155386</v>
+        <v>-16.8617864811157</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-9.874611507814427</v>
       </c>
       <c r="E3">
-        <v>-23.96366761864741</v>
+        <v>-26.78979314888032</v>
       </c>
       <c r="F3">
-        <v>-3.481113925056691</v>
+        <v>-3.385546834530518</v>
       </c>
       <c r="G3">
-        <v>-15.48927733762588</v>
+        <v>-16.69301155897812</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-9.621810991340741</v>
       </c>
       <c r="E4">
-        <v>-25.05918699363501</v>
+        <v>-26.88694250176687</v>
       </c>
       <c r="F4">
-        <v>-3.221721441646263</v>
+        <v>-3.303773717995762</v>
       </c>
       <c r="G4">
-        <v>-15.66587176832722</v>
+        <v>-15.72131512974616</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-9.215866470256376</v>
       </c>
       <c r="E5">
-        <v>-25.01880659090861</v>
+        <v>-27.71343429290679</v>
       </c>
       <c r="F5">
-        <v>-3.340787658655052</v>
+        <v>-3.16757437799487</v>
       </c>
       <c r="G5">
-        <v>-15.47516944781027</v>
+        <v>-16.17383856532745</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-8.681058100082812</v>
       </c>
       <c r="E6">
-        <v>-25.28410724064798</v>
+        <v>-27.11413151425768</v>
       </c>
       <c r="F6">
-        <v>-3.314625330972436</v>
+        <v>-3.113525061697008</v>
       </c>
       <c r="G6">
-        <v>-15.8761427235268</v>
+        <v>-16.65881693410298</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-8.046355547254976</v>
       </c>
       <c r="E7">
-        <v>-25.31331589799745</v>
+        <v>-27.66913676016376</v>
       </c>
       <c r="F7">
-        <v>-3.185846506165821</v>
+        <v>-3.265561958072023</v>
       </c>
       <c r="G7">
-        <v>-15.34701657471232</v>
+        <v>-16.33888581318782</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-7.33632791358936</v>
       </c>
       <c r="E8">
-        <v>-25.85958571754272</v>
+        <v>-28.20615037883735</v>
       </c>
       <c r="F8">
-        <v>-3.183885760523395</v>
+        <v>-3.251232030370995</v>
       </c>
       <c r="G8">
-        <v>-15.40849175010381</v>
+        <v>-16.2180028980941</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-6.5756138755018</v>
       </c>
       <c r="E9">
-        <v>-26.41559175620449</v>
+        <v>-28.8681181808046</v>
       </c>
       <c r="F9">
-        <v>-3.134788424559468</v>
+        <v>-3.109548069796168</v>
       </c>
       <c r="G9">
-        <v>-15.41180891673416</v>
+        <v>-16.04773657519107</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-5.797051364101799</v>
       </c>
       <c r="E10">
-        <v>-26.67328909808498</v>
+        <v>-29.32612351346637</v>
       </c>
       <c r="F10">
-        <v>-3.149777732713126</v>
+        <v>-3.212903470643462</v>
       </c>
       <c r="G10">
-        <v>-15.40004489316036</v>
+        <v>-16.22208480074402</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-5.025898609567142</v>
       </c>
       <c r="E11">
-        <v>-27.51846537298055</v>
+        <v>-29.47230491867097</v>
       </c>
       <c r="F11">
-        <v>-3.041315446827572</v>
+        <v>-3.042824732235473</v>
       </c>
       <c r="G11">
-        <v>-14.59934807266838</v>
+        <v>-15.28995932234298</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-4.280800354593501</v>
       </c>
       <c r="E12">
-        <v>-28.50120763128112</v>
+        <v>-30.14018917192924</v>
       </c>
       <c r="F12">
-        <v>-2.836429538521351</v>
+        <v>-2.927858933870541</v>
       </c>
       <c r="G12">
-        <v>-14.48972928877204</v>
+        <v>-15.51035392580165</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-3.571251523393786</v>
       </c>
       <c r="E13">
-        <v>-28.70909175907724</v>
+        <v>-30.85926555960721</v>
       </c>
       <c r="F13">
-        <v>-2.866280586248634</v>
+        <v>-2.896917754641174</v>
       </c>
       <c r="G13">
-        <v>-14.56370342884705</v>
+        <v>-15.60110591066969</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-2.914490987230154</v>
       </c>
       <c r="E14">
-        <v>-29.22973494421311</v>
+        <v>-31.46541765519292</v>
       </c>
       <c r="F14">
-        <v>-2.717466039070508</v>
+        <v>-2.80325922261105</v>
       </c>
       <c r="G14">
-        <v>-14.17701184658694</v>
+        <v>-15.21363138438954</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-2.314273773245954</v>
       </c>
       <c r="E15">
-        <v>-30.40641136612917</v>
+        <v>-31.81932242736637</v>
       </c>
       <c r="F15">
-        <v>-2.731042980802392</v>
+        <v>-2.769360771753689</v>
       </c>
       <c r="G15">
-        <v>-13.4062738079526</v>
+        <v>-14.73634341290173</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-1.768060200970411</v>
       </c>
       <c r="E16">
-        <v>-30.80900855507009</v>
+        <v>-32.4167572104873</v>
       </c>
       <c r="F16">
-        <v>-2.242226689880015</v>
+        <v>-2.548453409509922</v>
       </c>
       <c r="G16">
-        <v>-13.60240542315395</v>
+        <v>-14.58505810284812</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-1.271344050699502</v>
       </c>
       <c r="E17">
-        <v>-31.748852579096</v>
+        <v>-33.48332831538087</v>
       </c>
       <c r="F17">
-        <v>-2.520211879646279</v>
+        <v>-2.349013188509705</v>
       </c>
       <c r="G17">
-        <v>-13.0102597294539</v>
+        <v>-14.59187948193179</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-0.8235460028021537</v>
       </c>
       <c r="E18">
-        <v>-32.18325097675579</v>
+        <v>-34.15458628177485</v>
       </c>
       <c r="F18">
-        <v>-2.149736984255242</v>
+        <v>-2.017293462058643</v>
       </c>
       <c r="G18">
-        <v>-12.23851528497562</v>
+        <v>-13.8169519479175</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-0.4196113011129641</v>
       </c>
       <c r="E19">
-        <v>-32.99774004753838</v>
+        <v>-34.65153649090259</v>
       </c>
       <c r="F19">
-        <v>-1.945319931899005</v>
+        <v>-2.024651021330308</v>
       </c>
       <c r="G19">
-        <v>-12.45597840035926</v>
+        <v>-13.5461774624422</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-0.05333099684684368</v>
       </c>
       <c r="E20">
-        <v>-33.11268856751207</v>
+        <v>-35.80500448352934</v>
       </c>
       <c r="F20">
-        <v>-2.05102789617025</v>
+        <v>-1.987517795765015</v>
       </c>
       <c r="G20">
-        <v>-12.01152110898441</v>
+        <v>-12.96360090062341</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>0.2753196341761151</v>
       </c>
       <c r="E21">
-        <v>-34.08967513534891</v>
+        <v>-36.01534304423761</v>
       </c>
       <c r="F21">
-        <v>-1.612074352691987</v>
+        <v>-1.62686153919936</v>
       </c>
       <c r="G21">
-        <v>-11.91813061932157</v>
+        <v>-13.03381426096581</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>0.5651521098780871</v>
       </c>
       <c r="E22">
-        <v>-34.34617243161736</v>
+        <v>-36.5054778999838</v>
       </c>
       <c r="F22">
-        <v>-1.566494264720346</v>
+        <v>-1.729489633466997</v>
       </c>
       <c r="G22">
-        <v>-11.56321034260185</v>
+        <v>-13.12878057030535</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>0.8158570522564123</v>
       </c>
       <c r="E23">
-        <v>-34.78468041943911</v>
+        <v>-36.85866038055303</v>
       </c>
       <c r="F23">
-        <v>-1.37405540500859</v>
+        <v>-1.698249413605219</v>
       </c>
       <c r="G23">
-        <v>-11.24476896717935</v>
+        <v>-12.55912837827188</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>1.029480169897609</v>
       </c>
       <c r="E24">
-        <v>-35.37694594948029</v>
+        <v>-37.13119753175665</v>
       </c>
       <c r="F24">
-        <v>-1.389002466424705</v>
+        <v>-1.451261732051713</v>
       </c>
       <c r="G24">
-        <v>-11.29304665277854</v>
+        <v>-12.3330644655772</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>1.203969034807015</v>
       </c>
       <c r="E25">
-        <v>-35.66655771192983</v>
+        <v>-37.83021957229166</v>
       </c>
       <c r="F25">
-        <v>-1.186090557639355</v>
+        <v>-1.530692225571352</v>
       </c>
       <c r="G25">
-        <v>-11.53029027775933</v>
+        <v>-12.47971501187584</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>1.3396715854318</v>
       </c>
       <c r="E26">
-        <v>-35.75398443112192</v>
+        <v>-37.50656727072646</v>
       </c>
       <c r="F26">
-        <v>-0.9607969899977647</v>
+        <v>-1.342536853699472</v>
       </c>
       <c r="G26">
-        <v>-11.0335859566837</v>
+        <v>-12.27486507499682</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>1.437663635767529</v>
       </c>
       <c r="E27">
-        <v>-35.9401228267332</v>
+        <v>-37.67448987964188</v>
       </c>
       <c r="F27">
-        <v>-0.9834238456052332</v>
+        <v>-1.329747689367651</v>
       </c>
       <c r="G27">
-        <v>-11.02458458336242</v>
+        <v>-13.01577840886786</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>1.499650950890224</v>
       </c>
       <c r="E28">
-        <v>-35.92365729524131</v>
+        <v>-38.44677130843598</v>
       </c>
       <c r="F28">
-        <v>-1.404194724592048</v>
+        <v>-1.514259073034615</v>
       </c>
       <c r="G28">
-        <v>-11.12161005202738</v>
+        <v>-12.88830254233269</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>1.524900608254281</v>
       </c>
       <c r="E29">
-        <v>-35.97897939795602</v>
+        <v>-38.06547606122714</v>
       </c>
       <c r="F29">
-        <v>-1.143235798422925</v>
+        <v>-1.36734728578072</v>
       </c>
       <c r="G29">
-        <v>-11.41708948358949</v>
+        <v>-12.44498407862334</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>1.51336419583143</v>
       </c>
       <c r="E30">
-        <v>-35.42958493134545</v>
+        <v>-37.9758892599334</v>
       </c>
       <c r="F30">
-        <v>-1.001430896207289</v>
+        <v>-1.138361684624853</v>
       </c>
       <c r="G30">
-        <v>-11.7158728395998</v>
+        <v>-12.86601263921678</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>1.463727573704643</v>
       </c>
       <c r="E31">
-        <v>-35.27062870096521</v>
+        <v>-37.83421368636643</v>
       </c>
       <c r="F31">
-        <v>-1.23995431963899</v>
+        <v>-1.441035536464153</v>
       </c>
       <c r="G31">
-        <v>-11.47276292792342</v>
+        <v>-13.08617053866939</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>1.372655122549157</v>
       </c>
       <c r="E32">
-        <v>-35.18509035543433</v>
+        <v>-37.03604070743347</v>
       </c>
       <c r="F32">
-        <v>-1.225941656653233</v>
+        <v>-1.486497996264595</v>
       </c>
       <c r="G32">
-        <v>-11.42646825910225</v>
+        <v>-12.95942630269839</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>1.236272426372995</v>
       </c>
       <c r="E33">
-        <v>-35.53360397930164</v>
+        <v>-37.40697480611276</v>
       </c>
       <c r="F33">
-        <v>-1.407456835424272</v>
+        <v>-1.561294602532974</v>
       </c>
       <c r="G33">
-        <v>-11.64349107192917</v>
+        <v>-12.81860893763995</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>1.052760307515056</v>
       </c>
       <c r="E34">
-        <v>-34.56195874655686</v>
+        <v>-36.2600549869011</v>
       </c>
       <c r="F34">
-        <v>-1.205929956936403</v>
+        <v>-1.490668826137691</v>
       </c>
       <c r="G34">
-        <v>-11.46254989493477</v>
+        <v>-13.09681394257814</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>0.8183642603397455</v>
       </c>
       <c r="E35">
-        <v>-33.94300918342548</v>
+        <v>-36.21114520338126</v>
       </c>
       <c r="F35">
-        <v>-1.064311437386396</v>
+        <v>-1.392537938499853</v>
       </c>
       <c r="G35">
-        <v>-11.83401958880531</v>
+        <v>-12.82066478641984</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>0.5303471434842665</v>
       </c>
       <c r="E36">
-        <v>-33.87486244232105</v>
+        <v>-36.2506040616471</v>
       </c>
       <c r="F36">
-        <v>-1.323573038747183</v>
+        <v>-1.493053695890351</v>
       </c>
       <c r="G36">
-        <v>-11.83402620989639</v>
+        <v>-12.83769754321939</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>0.1874174923388958</v>
       </c>
       <c r="E37">
-        <v>-33.84134947042729</v>
+        <v>-35.19710439697667</v>
       </c>
       <c r="F37">
-        <v>-1.388411012099106</v>
+        <v>-1.223663646295535</v>
       </c>
       <c r="G37">
-        <v>-11.77361537489577</v>
+        <v>-13.28828265438743</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-0.2070500435631211</v>
       </c>
       <c r="E38">
-        <v>-33.08110472554558</v>
+        <v>-34.88960969067084</v>
       </c>
       <c r="F38">
-        <v>-1.385801654780287</v>
+        <v>-1.302081874848953</v>
       </c>
       <c r="G38">
-        <v>-12.3208319998096</v>
+        <v>-13.5869319333034</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-0.655313478843823</v>
       </c>
       <c r="E39">
-        <v>-32.67475116741529</v>
+        <v>-34.25227905154232</v>
       </c>
       <c r="F39">
-        <v>-1.096984732855018</v>
+        <v>-1.2299559250872</v>
       </c>
       <c r="G39">
-        <v>-11.94664434805131</v>
+        <v>-13.33036961982819</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-1.154785878595305</v>
       </c>
       <c r="E40">
-        <v>-31.90377620337241</v>
+        <v>-34.61412450288822</v>
       </c>
       <c r="F40">
-        <v>-1.071373269495262</v>
+        <v>-1.36285256425313</v>
       </c>
       <c r="G40">
-        <v>-12.27774193907044</v>
+        <v>-13.28119146584231</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-1.700007136974611</v>
       </c>
       <c r="E41">
-        <v>-32.17909836609076</v>
+        <v>-33.69617338645239</v>
       </c>
       <c r="F41">
-        <v>-1.118675533297323</v>
+        <v>-1.143066811472754</v>
       </c>
       <c r="G41">
-        <v>-11.56721610270436</v>
+        <v>-13.0178044627379</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-2.282081341461123</v>
       </c>
       <c r="E42">
-        <v>-31.14060380004475</v>
+        <v>-32.7502634714932</v>
       </c>
       <c r="F42">
-        <v>-1.148495931430702</v>
+        <v>-0.9982333980324828</v>
       </c>
       <c r="G42">
-        <v>-12.23557883108228</v>
+        <v>-12.75943293612548</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-2.897237011479077</v>
       </c>
       <c r="E43">
-        <v>-31.45655316732291</v>
+        <v>-32.44135814553398</v>
       </c>
       <c r="F43">
-        <v>-1.139620803077108</v>
+        <v>-0.8722072381053716</v>
       </c>
       <c r="G43">
-        <v>-11.84056122679091</v>
+        <v>-12.61902938925945</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-3.536575812028092</v>
       </c>
       <c r="E44">
-        <v>-30.27754005281889</v>
+        <v>-32.24028257840839</v>
       </c>
       <c r="F44">
-        <v>-1.057041685059428</v>
+        <v>-1.02572442702919</v>
       </c>
       <c r="G44">
-        <v>-11.8616692651493</v>
+        <v>-13.39915613504316</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-4.186310547432459</v>
       </c>
       <c r="E45">
-        <v>-30.37877861773436</v>
+        <v>-31.16716103586273</v>
       </c>
       <c r="F45">
-        <v>-0.8747213331728682</v>
+        <v>-1.124229736733093</v>
       </c>
       <c r="G45">
-        <v>-12.30679859726863</v>
+        <v>-13.22447519966352</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-4.834978174354005</v>
       </c>
       <c r="E46">
-        <v>-28.73505350056321</v>
+        <v>-31.24697991872193</v>
       </c>
       <c r="F46">
-        <v>-1.006102888359078</v>
+        <v>-0.967732910261405</v>
       </c>
       <c r="G46">
-        <v>-11.97344983528279</v>
+        <v>-13.44873486503929</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-5.473775920382969</v>
       </c>
       <c r="E47">
-        <v>-28.83896386514321</v>
+        <v>-31.0879716108906</v>
       </c>
       <c r="F47">
-        <v>-0.9339172961443236</v>
+        <v>-0.9603306191499886</v>
       </c>
       <c r="G47">
-        <v>-12.11293967157998</v>
+        <v>-13.38249415934401</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-6.091751566272216</v>
       </c>
       <c r="E48">
-        <v>-27.72640384246476</v>
+        <v>-30.48528832639477</v>
       </c>
       <c r="F48">
-        <v>-0.87752701356615</v>
+        <v>-0.9922426449754368</v>
       </c>
       <c r="G48">
-        <v>-12.31422415091321</v>
+        <v>-13.23525764648493</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-6.671425437557331</v>
       </c>
       <c r="E49">
-        <v>-27.96768999454144</v>
+        <v>-29.54567072606924</v>
       </c>
       <c r="F49">
-        <v>-0.8486004238603913</v>
+        <v>-0.9071858800559836</v>
       </c>
       <c r="G49">
-        <v>-12.1274994508617</v>
+        <v>-13.18679788088108</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-7.204590249638378</v>
       </c>
       <c r="E50">
-        <v>-27.2965701466047</v>
+        <v>-28.52514967335967</v>
       </c>
       <c r="F50">
-        <v>-0.9370982269710737</v>
+        <v>-0.9684411643907985</v>
       </c>
       <c r="G50">
-        <v>-12.0947912609337</v>
+        <v>-13.21613262490456</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-7.683334382752331</v>
       </c>
       <c r="E51">
-        <v>-26.59261886211234</v>
+        <v>-29.47600694617224</v>
       </c>
       <c r="F51">
-        <v>-0.9780162631997581</v>
+        <v>-0.8677655320915606</v>
       </c>
       <c r="G51">
-        <v>-12.4890606819332</v>
+        <v>-13.46138445954485</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-8.099885389527286</v>
       </c>
       <c r="E52">
-        <v>-26.70736133651869</v>
+        <v>-27.80765825158438</v>
       </c>
       <c r="F52">
-        <v>-0.7372048890015249</v>
+        <v>-0.7509044291090232</v>
       </c>
       <c r="G52">
-        <v>-12.28475698506816</v>
+        <v>-13.2007849357845</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-8.442979776757509</v>
       </c>
       <c r="E53">
-        <v>-26.005574662602</v>
+        <v>-27.47050430476531</v>
       </c>
       <c r="F53">
-        <v>-0.9860298894544405</v>
+        <v>-0.9013558302750806</v>
       </c>
       <c r="G53">
-        <v>-12.49090796634411</v>
+        <v>-13.17418470237645</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-8.711382214197373</v>
       </c>
       <c r="E54">
-        <v>-25.29938631194986</v>
+        <v>-27.47997787238936</v>
       </c>
       <c r="F54">
-        <v>-0.8767889382102557</v>
+        <v>-0.6980968355479575</v>
       </c>
       <c r="G54">
-        <v>-12.32250713585247</v>
+        <v>-13.39961630087312</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-8.906118004604513</v>
       </c>
       <c r="E55">
-        <v>-25.08242712224237</v>
+        <v>-26.86413710666424</v>
       </c>
       <c r="F55">
-        <v>-0.9564621433789149</v>
+        <v>-0.8906963985358566</v>
       </c>
       <c r="G55">
-        <v>-12.18586436871905</v>
+        <v>-13.65189973423882</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-9.025706886852488</v>
       </c>
       <c r="E56">
-        <v>-24.72804233182411</v>
+        <v>-26.67880930790033</v>
       </c>
       <c r="F56">
-        <v>-0.8592880200913106</v>
+        <v>-0.8989046911301969</v>
       </c>
       <c r="G56">
-        <v>-12.21384509961697</v>
+        <v>-13.48483967469058</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-9.068494574059137</v>
       </c>
       <c r="E57">
-        <v>-23.9629566482282</v>
+        <v>-26.77231776768472</v>
       </c>
       <c r="F57">
-        <v>-1.052288512902165</v>
+        <v>-0.7347032194450704</v>
       </c>
       <c r="G57">
-        <v>-12.46305303617669</v>
+        <v>-13.64949958872285</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-9.038271140756198</v>
       </c>
       <c r="E58">
-        <v>-23.99069355152518</v>
+        <v>-25.84518969867234</v>
       </c>
       <c r="F58">
-        <v>-1.079702503730411</v>
+        <v>-0.943860190080126</v>
       </c>
       <c r="G58">
-        <v>-12.52080550310927</v>
+        <v>-13.90493797198748</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-8.94351905124674</v>
       </c>
       <c r="E59">
-        <v>-23.49825370250909</v>
+        <v>-25.74121593545623</v>
       </c>
       <c r="F59">
-        <v>-1.004022029443246</v>
+        <v>-1.034588786606548</v>
       </c>
       <c r="G59">
-        <v>-12.78968801180888</v>
+        <v>-13.5999440325455</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-8.786297384579377</v>
       </c>
       <c r="E60">
-        <v>-23.54271426031639</v>
+        <v>-24.61083636755759</v>
       </c>
       <c r="F60">
-        <v>-1.112467747980743</v>
+        <v>-1.283504907473771</v>
       </c>
       <c r="G60">
-        <v>-12.71188357054493</v>
+        <v>-14.317544504729</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-8.569946913787359</v>
       </c>
       <c r="E61">
-        <v>-23.15630410171589</v>
+        <v>-25.12987647289474</v>
       </c>
       <c r="F61">
-        <v>-1.035573715448476</v>
+        <v>-1.082090686952682</v>
       </c>
       <c r="G61">
-        <v>-12.84867531222761</v>
+        <v>-14.20052003046131</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-8.301907295206302</v>
       </c>
       <c r="E62">
-        <v>-22.29483890581474</v>
+        <v>-24.91342900075012</v>
       </c>
       <c r="F62">
-        <v>-1.353890457322242</v>
+        <v>-1.17729495255643</v>
       </c>
       <c r="G62">
-        <v>-12.43852851482177</v>
+        <v>-14.02959656426873</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-7.991107331095101</v>
       </c>
       <c r="E63">
-        <v>-22.97088120499782</v>
+        <v>-24.85589021000866</v>
       </c>
       <c r="F63">
-        <v>-1.172807686335465</v>
+        <v>-1.347871539773501</v>
       </c>
       <c r="G63">
-        <v>-12.91288003241624</v>
+        <v>-14.02468040414292</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-7.639298082392571</v>
       </c>
       <c r="E64">
-        <v>-22.32897907135856</v>
+        <v>-24.30579835840091</v>
       </c>
       <c r="F64">
-        <v>-1.208267609747103</v>
+        <v>-1.359522527293876</v>
       </c>
       <c r="G64">
-        <v>-13.24369953761007</v>
+        <v>-14.20586490623446</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-7.247928534999438</v>
       </c>
       <c r="E65">
-        <v>-21.96691398902329</v>
+        <v>-24.67918915422936</v>
       </c>
       <c r="F65">
-        <v>-1.459299380961076</v>
+        <v>-1.432145497497309</v>
       </c>
       <c r="G65">
-        <v>-12.89036170165812</v>
+        <v>-14.31270448715059</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-6.823940160696911</v>
       </c>
       <c r="E66">
-        <v>-21.37160079597495</v>
+        <v>-24.08177927771547</v>
       </c>
       <c r="F66">
-        <v>-1.469344164087423</v>
+        <v>-1.587644141248624</v>
       </c>
       <c r="G66">
-        <v>-13.15972092891538</v>
+        <v>-14.10678027824407</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-6.371397427178302</v>
       </c>
       <c r="E67">
-        <v>-21.77536406697284</v>
+        <v>-24.27031323607681</v>
       </c>
       <c r="F67">
-        <v>-1.558224672938199</v>
+        <v>-1.572939791481529</v>
       </c>
       <c r="G67">
-        <v>-13.13726880906804</v>
+        <v>-13.97572571198094</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-5.890831101806721</v>
       </c>
       <c r="E68">
-        <v>-22.43984517201435</v>
+        <v>-24.2891426310007</v>
       </c>
       <c r="F68">
-        <v>-1.681678752079618</v>
+        <v>-1.709042212496294</v>
       </c>
       <c r="G68">
-        <v>-12.60533035181794</v>
+        <v>-14.3540962380281</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-5.378708341408809</v>
       </c>
       <c r="E69">
-        <v>-21.89522371700787</v>
+        <v>-24.0487350028815</v>
       </c>
       <c r="F69">
-        <v>-1.87490953102845</v>
+        <v>-1.87556062780705</v>
       </c>
       <c r="G69">
-        <v>-12.92741663787918</v>
+        <v>-14.52915292032645</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-4.840233356507309</v>
       </c>
       <c r="E70">
-        <v>-21.88889291034514</v>
+        <v>-24.25252991864868</v>
       </c>
       <c r="F70">
-        <v>-1.903951263803198</v>
+        <v>-1.867096369685245</v>
       </c>
       <c r="G70">
-        <v>-12.5743635088436</v>
+        <v>-13.79448327534246</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-4.274064910586005</v>
       </c>
       <c r="E71">
-        <v>-21.67474137452241</v>
+        <v>-23.37203154649329</v>
       </c>
       <c r="F71">
-        <v>-2.028772977526638</v>
+        <v>-2.060530098647763</v>
       </c>
       <c r="G71">
-        <v>-12.73140916813555</v>
+        <v>-13.89534070046913</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-3.676920744349035</v>
       </c>
       <c r="E72">
-        <v>-21.61242051522885</v>
+        <v>-23.79104218947501</v>
       </c>
       <c r="F72">
-        <v>-2.122705699167089</v>
+        <v>-2.093943126207084</v>
       </c>
       <c r="G72">
-        <v>-12.76859321563264</v>
+        <v>-13.64773010213211</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-3.042186672175529</v>
       </c>
       <c r="E73">
-        <v>-21.5714197115634</v>
+        <v>-23.75332905793913</v>
       </c>
       <c r="F73">
-        <v>-2.040032147265489</v>
+        <v>-1.967187174598106</v>
       </c>
       <c r="G73">
-        <v>-12.53101853609792</v>
+        <v>-13.92893115078335</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-2.37067118853501</v>
       </c>
       <c r="E74">
-        <v>-22.30860999527206</v>
+        <v>-24.22683082865516</v>
       </c>
       <c r="F74">
-        <v>-2.144294610418849</v>
+        <v>-2.395176447132916</v>
       </c>
       <c r="G74">
-        <v>-12.51967991762592</v>
+        <v>-13.86221703707595</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-1.661324761074361</v>
       </c>
       <c r="E75">
-        <v>-22.6754979024255</v>
+        <v>-24.24199668810684</v>
       </c>
       <c r="F75">
-        <v>-2.075833358047081</v>
+        <v>-2.225928561229935</v>
       </c>
       <c r="G75">
-        <v>-12.00054333997619</v>
+        <v>-13.62388424261274</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-0.9098097258958027</v>
       </c>
       <c r="E76">
-        <v>-22.3030852569827</v>
+        <v>-24.52371758459802</v>
       </c>
       <c r="F76">
-        <v>-2.399564309265545</v>
+        <v>-2.476802942637376</v>
       </c>
       <c r="G76">
-        <v>-12.52839327348528</v>
+        <v>-13.27103140158229</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-0.1150121795045431</v>
       </c>
       <c r="E77">
-        <v>-22.10704761719065</v>
+        <v>-24.76351386872619</v>
       </c>
       <c r="F77">
-        <v>-2.515766031795454</v>
+        <v>-2.407451195307599</v>
       </c>
       <c r="G77">
-        <v>-12.11855104626905</v>
+        <v>-13.66456919201761</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>0.7188353634685301</v>
       </c>
       <c r="E78">
-        <v>-22.83565191418077</v>
+        <v>-25.32843647270906</v>
       </c>
       <c r="F78">
-        <v>-2.528951155745814</v>
+        <v>-2.450792206189472</v>
       </c>
       <c r="G78">
-        <v>-11.91497566942265</v>
+        <v>-12.85501500693532</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>1.580486802642429</v>
       </c>
       <c r="E79">
-        <v>-23.39539847237287</v>
+        <v>-25.19559368769405</v>
       </c>
       <c r="F79">
-        <v>-2.362310142059443</v>
+        <v>-2.633420710749873</v>
       </c>
       <c r="G79">
-        <v>-11.42812022132635</v>
+        <v>-13.24630824749501</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>2.466544559785083</v>
       </c>
       <c r="E80">
-        <v>-23.79395852673595</v>
+        <v>-25.1785032267891</v>
       </c>
       <c r="F80">
-        <v>-2.380803444326942</v>
+        <v>-2.739254586866344</v>
       </c>
       <c r="G80">
-        <v>-11.58847642615756</v>
+        <v>-12.76335924313505</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>3.363111739726919</v>
       </c>
       <c r="E81">
-        <v>-24.27434810641764</v>
+        <v>-25.72055703703324</v>
       </c>
       <c r="F81">
-        <v>-2.720044746795423</v>
+        <v>-2.721127422990882</v>
       </c>
       <c r="G81">
-        <v>-11.16269392216974</v>
+        <v>-12.92421202979716</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>4.253273640684679</v>
       </c>
       <c r="E82">
-        <v>-24.41836263680957</v>
+        <v>-26.78073620086498</v>
       </c>
       <c r="F82">
-        <v>-2.645606823612457</v>
+        <v>-2.779370763449118</v>
       </c>
       <c r="G82">
-        <v>-11.19887487436843</v>
+        <v>-12.48823966663946</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>5.1148109588817</v>
       </c>
       <c r="E83">
-        <v>-25.36587789580448</v>
+        <v>-27.20254091230943</v>
       </c>
       <c r="F83">
-        <v>-2.568935621911543</v>
+        <v>-2.858915571670344</v>
       </c>
       <c r="G83">
-        <v>-10.72105721559435</v>
+        <v>-12.04775171936619</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>5.934188181296006</v>
       </c>
       <c r="E84">
-        <v>-26.10193606101122</v>
+        <v>-27.48829215066744</v>
       </c>
       <c r="F84">
-        <v>-2.932670091746</v>
+        <v>-2.574426041057298</v>
       </c>
       <c r="G84">
-        <v>-10.75455331536069</v>
+        <v>-12.28852107534631</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>6.690703288323722</v>
       </c>
       <c r="E85">
-        <v>-26.32433394800192</v>
+        <v>-28.17244494679826</v>
       </c>
       <c r="F85">
-        <v>-2.908388986435141</v>
+        <v>-2.890660267280426</v>
       </c>
       <c r="G85">
-        <v>-11.13258782103561</v>
+        <v>-12.37805146891036</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>7.363360144571192</v>
       </c>
       <c r="E86">
-        <v>-27.32076125475367</v>
+        <v>-28.92826990104848</v>
       </c>
       <c r="F86">
-        <v>-2.915440049767771</v>
+        <v>-3.044445018875349</v>
       </c>
       <c r="G86">
-        <v>-10.6872995827304</v>
+        <v>-12.26577431694598</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>7.93277668102203</v>
       </c>
       <c r="E87">
-        <v>-28.15318081836963</v>
+        <v>-29.83641687125771</v>
       </c>
       <c r="F87">
-        <v>-2.933544847723357</v>
+        <v>-3.094716979816445</v>
       </c>
       <c r="G87">
-        <v>-10.45334995056118</v>
+        <v>-12.03361900045905</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>8.385616794558343</v>
       </c>
       <c r="E88">
-        <v>-28.38272463734443</v>
+        <v>-30.93650094804504</v>
       </c>
       <c r="F88">
-        <v>-3.11500535424581</v>
+        <v>-3.163536915273625</v>
       </c>
       <c r="G88">
-        <v>-10.5500178803079</v>
+        <v>-11.99080702554519</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>8.709194992362978</v>
       </c>
       <c r="E89">
-        <v>-30.02936835601353</v>
+        <v>-31.6808394279748</v>
       </c>
       <c r="F89">
-        <v>-3.218837066349715</v>
+        <v>-3.207514940688251</v>
       </c>
       <c r="G89">
-        <v>-10.9430392256391</v>
+        <v>-11.79938797191899</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>8.891629389041483</v>
       </c>
       <c r="E90">
-        <v>-31.25590327675404</v>
+        <v>-32.2592410348415</v>
       </c>
       <c r="F90">
-        <v>-3.298372762529509</v>
+        <v>-3.218935642070648</v>
       </c>
       <c r="G90">
-        <v>-10.79993758415856</v>
+        <v>-12.20019572035855</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>8.928150926920653</v>
       </c>
       <c r="E91">
-        <v>-32.22679451857655</v>
+        <v>-33.99121026076312</v>
       </c>
       <c r="F91">
-        <v>-3.534750714387959</v>
+        <v>-3.216765319475313</v>
       </c>
       <c r="G91">
-        <v>-10.47885770394127</v>
+        <v>-11.93306449024922</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>8.82010854602238</v>
       </c>
       <c r="E92">
-        <v>-33.7796059915697</v>
+        <v>-35.40361639714846</v>
       </c>
       <c r="F92">
-        <v>-3.492438535820364</v>
+        <v>-3.544618226890107</v>
       </c>
       <c r="G92">
-        <v>-10.72405325930739</v>
+        <v>-12.49236791692693</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>8.574369039658624</v>
       </c>
       <c r="E93">
-        <v>-35.05222266381227</v>
+        <v>-36.90650597268107</v>
       </c>
       <c r="F93">
-        <v>-3.279578762894794</v>
+        <v>-3.526404084437352</v>
       </c>
       <c r="G93">
-        <v>-10.69226871158484</v>
+        <v>-12.31313498143079</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>8.198570134077587</v>
       </c>
       <c r="E94">
-        <v>-36.51369028759672</v>
+        <v>-37.94140493036499</v>
       </c>
       <c r="F94">
-        <v>-3.362320240923423</v>
+        <v>-3.604551436850054</v>
       </c>
       <c r="G94">
-        <v>-10.89705905864416</v>
+        <v>-12.35906880078818</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>7.708333482287452</v>
       </c>
       <c r="E95">
-        <v>-38.37825776093693</v>
+        <v>-39.15869723565584</v>
       </c>
       <c r="F95">
-        <v>-3.701448057057721</v>
+        <v>-3.670308069651682</v>
       </c>
       <c r="G95">
-        <v>-10.88899456971049</v>
+        <v>-12.83257612927014</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>7.117923247042952</v>
       </c>
       <c r="E96">
-        <v>-38.92315998133189</v>
+        <v>-41.63327280019929</v>
       </c>
       <c r="F96">
-        <v>-3.77439243381344</v>
+        <v>-4.022039495819574</v>
       </c>
       <c r="G96">
-        <v>-11.42967948827534</v>
+        <v>-12.3761247314065</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>6.457382481434156</v>
       </c>
       <c r="E97">
-        <v>-41.68568309412706</v>
+        <v>-42.74540488208403</v>
       </c>
       <c r="F97">
-        <v>-3.870668606836409</v>
+        <v>-4.01786618084427</v>
       </c>
       <c r="G97">
-        <v>-11.74196655954033</v>
+        <v>-12.90979791451918</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>5.723586289362863</v>
       </c>
       <c r="E98">
-        <v>-43.06316337472825</v>
+        <v>-44.3498794507937</v>
       </c>
       <c r="F98">
-        <v>-3.92346874509085</v>
+        <v>-4.119054572565841</v>
       </c>
       <c r="G98">
-        <v>-12.09981997960785</v>
+        <v>-13.17918362614075</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>4.958641935142365</v>
       </c>
       <c r="E99">
-        <v>-45.16137067178321</v>
+        <v>-45.79647330169995</v>
       </c>
       <c r="F99">
-        <v>-3.904426235235295</v>
+        <v>-4.080473360780454</v>
       </c>
       <c r="G99">
-        <v>-12.015195814533</v>
+        <v>-13.30205121328526</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>4.135306089049946</v>
       </c>
       <c r="E100">
-        <v>-46.72175148908019</v>
+        <v>-47.90496929170033</v>
       </c>
       <c r="F100">
-        <v>-3.923228518544038</v>
+        <v>-4.393459558417205</v>
       </c>
       <c r="G100">
-        <v>-11.99913966866754</v>
+        <v>-14.51358176938249</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>3.333670609296535</v>
       </c>
       <c r="E101">
-        <v>-48.51679216886215</v>
+        <v>-49.38276093216393</v>
       </c>
       <c r="F101">
-        <v>-4.274177965883688</v>
+        <v>-4.445090041898893</v>
       </c>
       <c r="G101">
-        <v>-12.5823882712308</v>
+        <v>-13.82132021275657</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>2.430249117969695</v>
       </c>
       <c r="E102">
-        <v>-50.58978379052389</v>
+        <v>-51.18117758931859</v>
       </c>
       <c r="F102">
-        <v>-4.284277421258619</v>
+        <v>-4.645424899694134</v>
       </c>
       <c r="G102">
-        <v>-12.61398080731206</v>
+        <v>-14.09705555072246</v>
       </c>
     </row>
   </sheetData>
